--- a/KiCad/LaunchController2.0/BOM_LaunchController2.0.xlsx
+++ b/KiCad/LaunchController2.0/BOM_LaunchController2.0.xlsx
@@ -10,12 +10,25 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{AB23BE3D-1396-4B94-88AE-4BB647613D3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="27096" windowHeight="16296" xr2:uid="{67BE81D0-99D5-4A12-A1A5-9B30203A7372}"/>
+    <workbookView xWindow="33465" yWindow="-705" windowWidth="38670" windowHeight="21150" xr2:uid="{67BE81D0-99D5-4A12-A1A5-9B30203A7372}"/>
   </bookViews>
   <sheets>
     <sheet name="LaunchController2.0" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1277,14 +1290,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="42">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
@@ -1714,7 +1724,7 @@
       <c r="J1" t="s">
         <v>202</v>
       </c>
-      <c r="K1" s="4" t="b">
+      <c r="K1" s="3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1734,25 +1744,25 @@
       <c r="E2" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="3">
-        <v>100</v>
-      </c>
-      <c r="G2" s="3">
+      <c r="F2" s="2">
+        <v>100</v>
+      </c>
+      <c r="G2" s="2">
         <f>F2</f>
         <v>100</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
       </c>
-      <c r="I2" s="3">
+      <c r="I2" s="2">
         <f>SUMIF(H2,FALSE,G2)</f>
         <v>0</v>
       </c>
-      <c r="J2" s="3">
+      <c r="J2" s="2">
         <f>SUM(I2:I61)</f>
         <v>15049</v>
       </c>
-      <c r="K2" s="4" t="b">
+      <c r="K2" s="3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1772,17 +1782,17 @@
       <c r="E3" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="3">
-        <v>100</v>
-      </c>
-      <c r="G3" s="3">
+      <c r="F3" s="2">
+        <v>100</v>
+      </c>
+      <c r="G3" s="2">
         <f t="shared" ref="G3:G8" si="0">F3</f>
         <v>100</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3" s="2">
         <f t="shared" ref="I3:I61" si="1">SUMIF(H3,FALSE,G3)</f>
         <v>100</v>
       </c>
@@ -1803,17 +1813,17 @@
       <c r="E4" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="3">
-        <v>100</v>
-      </c>
-      <c r="G4" s="3">
+      <c r="F4" s="2">
+        <v>100</v>
+      </c>
+      <c r="G4" s="2">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="2">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
@@ -1834,17 +1844,17 @@
       <c r="E5" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="3">
-        <v>100</v>
-      </c>
-      <c r="G5" s="3">
+      <c r="F5" s="2">
+        <v>100</v>
+      </c>
+      <c r="G5" s="2">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1865,17 +1875,17 @@
       <c r="E6" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="3">
-        <v>100</v>
-      </c>
-      <c r="G6" s="3">
+      <c r="F6" s="2">
+        <v>100</v>
+      </c>
+      <c r="G6" s="2">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
       </c>
-      <c r="I6" s="3">
+      <c r="I6" s="2">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
@@ -1896,17 +1906,17 @@
       <c r="E7" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="3">
-        <v>100</v>
-      </c>
-      <c r="G7" s="3">
+      <c r="F7" s="2">
+        <v>100</v>
+      </c>
+      <c r="G7" s="2">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
-      <c r="I7" s="3">
+      <c r="I7" s="2">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
@@ -1927,17 +1937,17 @@
       <c r="E8" t="s">
         <v>25</v>
       </c>
-      <c r="F8" s="3">
-        <v>100</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="F8" s="2">
+        <v>100</v>
+      </c>
+      <c r="G8" s="2">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
       </c>
-      <c r="I8" s="3">
+      <c r="I8" s="2">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
@@ -1958,17 +1968,17 @@
       <c r="E9" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="2">
         <v>220</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="2">
         <f>F9*B9</f>
         <v>220</v>
       </c>
       <c r="H9" t="b">
         <v>0</v>
       </c>
-      <c r="I9" s="3">
+      <c r="I9" s="2">
         <f t="shared" si="1"/>
         <v>220</v>
       </c>
@@ -1989,17 +1999,17 @@
       <c r="E10" t="s">
         <v>31</v>
       </c>
-      <c r="F10" s="3">
-        <v>100</v>
-      </c>
-      <c r="G10" s="3">
+      <c r="F10" s="2">
+        <v>100</v>
+      </c>
+      <c r="G10" s="2">
         <f>F10</f>
         <v>100</v>
       </c>
       <c r="H10" t="b">
         <v>0</v>
       </c>
-      <c r="I10" s="3">
+      <c r="I10" s="2">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
@@ -2020,17 +2030,17 @@
       <c r="E11" t="s">
         <v>34</v>
       </c>
-      <c r="F11" s="3">
-        <v>100</v>
-      </c>
-      <c r="G11" s="3">
+      <c r="F11" s="2">
+        <v>100</v>
+      </c>
+      <c r="G11" s="2">
         <f t="shared" ref="G11:G18" si="2">F11</f>
         <v>100</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
       </c>
-      <c r="I11" s="3">
+      <c r="I11" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2051,17 +2061,17 @@
       <c r="E12" t="s">
         <v>37</v>
       </c>
-      <c r="F12" s="3">
-        <v>100</v>
-      </c>
-      <c r="G12" s="3">
+      <c r="F12" s="2">
+        <v>100</v>
+      </c>
+      <c r="G12" s="2">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2082,17 +2092,17 @@
       <c r="E13" t="s">
         <v>40</v>
       </c>
-      <c r="F13" s="3">
-        <v>100</v>
-      </c>
-      <c r="G13" s="3">
+      <c r="F13" s="2">
+        <v>100</v>
+      </c>
+      <c r="G13" s="2">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
       </c>
-      <c r="I13" s="3">
+      <c r="I13" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2113,17 +2123,17 @@
       <c r="E14" t="s">
         <v>43</v>
       </c>
-      <c r="F14" s="3">
-        <v>100</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="F14" s="2">
+        <v>100</v>
+      </c>
+      <c r="G14" s="2">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
       <c r="H14" t="b">
         <v>0</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="2">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
@@ -2144,17 +2154,17 @@
       <c r="E15" t="s">
         <v>46</v>
       </c>
-      <c r="F15" s="3">
-        <v>100</v>
-      </c>
-      <c r="G15" s="3">
+      <c r="F15" s="2">
+        <v>100</v>
+      </c>
+      <c r="G15" s="2">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
       </c>
-      <c r="I15" s="3">
+      <c r="I15" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2175,17 +2185,17 @@
       <c r="E16" t="s">
         <v>49</v>
       </c>
-      <c r="F16" s="3">
-        <v>100</v>
-      </c>
-      <c r="G16" s="3">
+      <c r="F16" s="2">
+        <v>100</v>
+      </c>
+      <c r="G16" s="2">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
       </c>
-      <c r="I16" s="3">
+      <c r="I16" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2206,17 +2216,17 @@
       <c r="E17" t="s">
         <v>34</v>
       </c>
-      <c r="F17" s="3">
-        <v>100</v>
-      </c>
-      <c r="G17" s="3">
+      <c r="F17" s="2">
+        <v>100</v>
+      </c>
+      <c r="G17" s="2">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
       </c>
-      <c r="I17" s="3">
+      <c r="I17" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2237,17 +2247,17 @@
       <c r="E18" t="s">
         <v>53</v>
       </c>
-      <c r="F18" s="3">
-        <v>100</v>
-      </c>
-      <c r="G18" s="3">
+      <c r="F18" s="2">
+        <v>100</v>
+      </c>
+      <c r="G18" s="2">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
       </c>
-      <c r="I18" s="3">
+      <c r="I18" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2268,17 +2278,17 @@
       <c r="E19" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19" s="2">
         <v>586</v>
       </c>
-      <c r="G19" s="3">
+      <c r="G19" s="2">
         <f>F19*B19</f>
         <v>1172</v>
       </c>
       <c r="H19" t="b">
         <v>0</v>
       </c>
-      <c r="I19" s="3">
+      <c r="I19" s="2">
         <f t="shared" si="1"/>
         <v>1172</v>
       </c>
@@ -2290,7 +2300,7 @@
       <c r="B20">
         <v>1</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" t="s">
         <v>181</v>
       </c>
       <c r="D20" t="s">
@@ -2299,17 +2309,17 @@
       <c r="E20" t="s">
         <v>8</v>
       </c>
-      <c r="F20" s="3">
-        <v>100</v>
-      </c>
-      <c r="G20" s="3">
+      <c r="F20" s="2">
+        <v>100</v>
+      </c>
+      <c r="G20" s="2">
         <f>F20</f>
         <v>100</v>
       </c>
       <c r="H20" t="b">
         <v>0</v>
       </c>
-      <c r="I20" s="3">
+      <c r="I20" s="2">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
@@ -2330,17 +2340,17 @@
       <c r="E21" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21" s="2">
         <v>160</v>
       </c>
-      <c r="G21" s="3">
+      <c r="G21" s="2">
         <f>F21*B21</f>
         <v>160</v>
       </c>
       <c r="H21" t="b">
         <v>0</v>
       </c>
-      <c r="I21" s="3">
+      <c r="I21" s="2">
         <f t="shared" si="1"/>
         <v>160</v>
       </c>
@@ -2361,17 +2371,17 @@
       <c r="E22" t="s">
         <v>64</v>
       </c>
-      <c r="F22" s="3">
-        <v>100</v>
-      </c>
-      <c r="G22" s="3">
+      <c r="F22" s="2">
+        <v>100</v>
+      </c>
+      <c r="G22" s="2">
         <f>F22*B22</f>
         <v>200</v>
       </c>
       <c r="H22" t="b">
         <v>0</v>
       </c>
-      <c r="I22" s="3">
+      <c r="I22" s="2">
         <f t="shared" si="1"/>
         <v>200</v>
       </c>
@@ -2392,17 +2402,17 @@
       <c r="E23" t="s">
         <v>68</v>
       </c>
-      <c r="F23" s="3">
-        <v>100</v>
-      </c>
-      <c r="G23" s="3">
+      <c r="F23" s="2">
+        <v>100</v>
+      </c>
+      <c r="G23" s="2">
         <f>F23*B23</f>
         <v>100</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
       </c>
-      <c r="I23" s="3">
+      <c r="I23" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2423,17 +2433,17 @@
       <c r="E24" t="s">
         <v>8</v>
       </c>
-      <c r="F24" s="3">
-        <v>100</v>
-      </c>
-      <c r="G24" s="3">
+      <c r="F24" s="2">
+        <v>100</v>
+      </c>
+      <c r="G24" s="2">
         <f>F24</f>
         <v>100</v>
       </c>
       <c r="H24" t="b">
         <v>0</v>
       </c>
-      <c r="I24" s="3">
+      <c r="I24" s="2">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
@@ -2454,17 +2464,17 @@
       <c r="E25" t="s">
         <v>74</v>
       </c>
-      <c r="F25" s="3">
+      <c r="F25" s="2">
         <v>2986</v>
       </c>
-      <c r="G25" s="3">
+      <c r="G25" s="2">
         <f>F25*B25</f>
         <v>2986</v>
       </c>
       <c r="H25" t="b">
         <v>0</v>
       </c>
-      <c r="I25" s="3">
+      <c r="I25" s="2">
         <f t="shared" si="1"/>
         <v>2986</v>
       </c>
@@ -2485,17 +2495,17 @@
       <c r="E26" t="s">
         <v>78</v>
       </c>
-      <c r="F26" s="3">
+      <c r="F26" s="2">
         <v>2800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="G26" s="2">
         <f>F26*B26</f>
         <v>2800</v>
       </c>
       <c r="H26" t="b">
         <v>0</v>
       </c>
-      <c r="I26" s="3">
+      <c r="I26" s="2">
         <f t="shared" si="1"/>
         <v>2800</v>
       </c>
@@ -2516,17 +2526,17 @@
       <c r="E27" t="s">
         <v>82</v>
       </c>
-      <c r="F27" s="3">
+      <c r="F27" s="2">
         <v>401</v>
       </c>
-      <c r="G27" s="3">
+      <c r="G27" s="2">
         <f t="shared" ref="G27:G61" si="3">F27*B27</f>
         <v>401</v>
       </c>
       <c r="H27" t="b">
         <v>0</v>
       </c>
-      <c r="I27" s="3">
+      <c r="I27" s="2">
         <f t="shared" si="1"/>
         <v>401</v>
       </c>
@@ -2547,14 +2557,14 @@
       <c r="E28" t="s">
         <v>86</v>
       </c>
-      <c r="F28" s="3">
-        <v>0</v>
-      </c>
-      <c r="G28" s="3">
+      <c r="F28" s="2">
+        <v>0</v>
+      </c>
+      <c r="G28" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I28" s="3">
+      <c r="I28" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2575,14 +2585,14 @@
       <c r="E29" t="s">
         <v>86</v>
       </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3">
+      <c r="F29" s="2">
+        <v>0</v>
+      </c>
+      <c r="G29" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I29" s="3">
+      <c r="I29" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2603,14 +2613,14 @@
       <c r="E30" t="s">
         <v>86</v>
       </c>
-      <c r="F30" s="3">
-        <v>0</v>
-      </c>
-      <c r="G30" s="3">
+      <c r="F30" s="2">
+        <v>0</v>
+      </c>
+      <c r="G30" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I30" s="3">
+      <c r="I30" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2631,14 +2641,14 @@
       <c r="E31" t="s">
         <v>86</v>
       </c>
-      <c r="F31" s="3">
-        <v>0</v>
-      </c>
-      <c r="G31" s="3">
+      <c r="F31" s="2">
+        <v>0</v>
+      </c>
+      <c r="G31" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I31" s="3">
+      <c r="I31" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2659,17 +2669,17 @@
       <c r="E32" t="s">
         <v>99</v>
       </c>
-      <c r="F32" s="3">
+      <c r="F32" s="2">
         <v>750</v>
       </c>
-      <c r="G32" s="3">
+      <c r="G32" s="2">
         <f t="shared" si="3"/>
         <v>750</v>
       </c>
       <c r="H32" t="b">
         <v>0</v>
       </c>
-      <c r="I32" s="3">
+      <c r="I32" s="2">
         <f t="shared" si="1"/>
         <v>750</v>
       </c>
@@ -2690,17 +2700,17 @@
       <c r="E33" t="s">
         <v>82</v>
       </c>
-      <c r="F33" s="3">
+      <c r="F33" s="2">
         <v>401</v>
       </c>
-      <c r="G33" s="3">
+      <c r="G33" s="2">
         <f t="shared" si="3"/>
         <v>401</v>
       </c>
       <c r="H33" t="b">
         <v>0</v>
       </c>
-      <c r="I33" s="3">
+      <c r="I33" s="2">
         <f t="shared" si="1"/>
         <v>401</v>
       </c>
@@ -2721,14 +2731,14 @@
       <c r="E34" t="s">
         <v>86</v>
       </c>
-      <c r="F34" s="3">
-        <v>0</v>
-      </c>
-      <c r="G34" s="3">
+      <c r="F34" s="2">
+        <v>0</v>
+      </c>
+      <c r="G34" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I34" s="3">
+      <c r="I34" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2749,17 +2759,17 @@
       <c r="E35" t="s">
         <v>99</v>
       </c>
-      <c r="F35" s="3">
+      <c r="F35" s="2">
         <v>750</v>
       </c>
-      <c r="G35" s="3">
+      <c r="G35" s="2">
         <f t="shared" si="3"/>
         <v>750</v>
       </c>
       <c r="H35" t="b">
         <v>0</v>
       </c>
-      <c r="I35" s="3">
+      <c r="I35" s="2">
         <f t="shared" si="1"/>
         <v>750</v>
       </c>
@@ -2780,17 +2790,17 @@
       <c r="E36" t="s">
         <v>82</v>
       </c>
-      <c r="F36" s="3">
+      <c r="F36" s="2">
         <v>401</v>
       </c>
-      <c r="G36" s="3">
+      <c r="G36" s="2">
         <f t="shared" si="3"/>
         <v>401</v>
       </c>
       <c r="H36" t="b">
         <v>0</v>
       </c>
-      <c r="I36" s="3">
+      <c r="I36" s="2">
         <f t="shared" si="1"/>
         <v>401</v>
       </c>
@@ -2811,17 +2821,17 @@
       <c r="E37" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="F37" s="3">
+      <c r="F37" s="2">
         <v>1050</v>
       </c>
-      <c r="G37" s="3">
+      <c r="G37" s="2">
         <f t="shared" si="3"/>
         <v>1050</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
       </c>
-      <c r="I37" s="3">
+      <c r="I37" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2842,17 +2852,17 @@
       <c r="E38" t="s">
         <v>82</v>
       </c>
-      <c r="F38" s="3">
+      <c r="F38" s="2">
         <v>401</v>
       </c>
-      <c r="G38" s="3">
+      <c r="G38" s="2">
         <f t="shared" si="3"/>
         <v>401</v>
       </c>
       <c r="H38" t="b">
         <v>0</v>
       </c>
-      <c r="I38" s="3">
+      <c r="I38" s="2">
         <f t="shared" si="1"/>
         <v>401</v>
       </c>
@@ -2873,17 +2883,17 @@
       <c r="E39" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="F39" s="3">
+      <c r="F39" s="2">
         <v>550</v>
       </c>
-      <c r="G39" s="3">
+      <c r="G39" s="2">
         <f t="shared" si="3"/>
         <v>550</v>
       </c>
       <c r="H39" t="b">
         <v>0</v>
       </c>
-      <c r="I39" s="3">
+      <c r="I39" s="2">
         <f t="shared" si="1"/>
         <v>550</v>
       </c>
@@ -2904,17 +2914,17 @@
       <c r="E40" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="F40" s="3">
-        <v>100</v>
-      </c>
-      <c r="G40" s="3">
+      <c r="F40" s="2">
+        <v>100</v>
+      </c>
+      <c r="G40" s="2">
         <f t="shared" si="3"/>
         <v>300</v>
       </c>
       <c r="H40" t="b">
         <v>0</v>
       </c>
-      <c r="I40" s="3">
+      <c r="I40" s="2">
         <f t="shared" si="1"/>
         <v>300</v>
       </c>
@@ -2935,17 +2945,17 @@
       <c r="E41" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="F41" s="3">
+      <c r="F41" s="2">
         <v>30</v>
       </c>
-      <c r="G41" s="3">
+      <c r="G41" s="2">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="H41" t="b">
         <v>0</v>
       </c>
-      <c r="I41" s="3">
+      <c r="I41" s="2">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
@@ -2966,17 +2976,17 @@
       <c r="E42" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="F42" s="3">
+      <c r="F42" s="2">
         <v>481</v>
       </c>
-      <c r="G42" s="3">
+      <c r="G42" s="2">
         <f t="shared" si="3"/>
         <v>962</v>
       </c>
       <c r="H42" t="b">
         <v>0</v>
       </c>
-      <c r="I42" s="3">
+      <c r="I42" s="2">
         <f t="shared" si="1"/>
         <v>962</v>
       </c>
@@ -2997,17 +3007,17 @@
       <c r="E43" t="s">
         <v>129</v>
       </c>
-      <c r="F43" s="3">
-        <v>100</v>
-      </c>
-      <c r="G43" s="3">
+      <c r="F43" s="2">
+        <v>100</v>
+      </c>
+      <c r="G43" s="2">
         <f t="shared" si="3"/>
         <v>200</v>
       </c>
       <c r="H43" t="b">
         <v>0</v>
       </c>
-      <c r="I43" s="3">
+      <c r="I43" s="2">
         <f t="shared" si="1"/>
         <v>200</v>
       </c>
@@ -3028,17 +3038,17 @@
       <c r="E44" t="s">
         <v>132</v>
       </c>
-      <c r="F44" s="3">
-        <v>100</v>
-      </c>
-      <c r="G44" s="3">
+      <c r="F44" s="2">
+        <v>100</v>
+      </c>
+      <c r="G44" s="2">
         <f t="shared" si="3"/>
         <v>200</v>
       </c>
       <c r="H44" t="b">
         <v>0</v>
       </c>
-      <c r="I44" s="3">
+      <c r="I44" s="2">
         <f t="shared" si="1"/>
         <v>200</v>
       </c>
@@ -3059,17 +3069,17 @@
       <c r="E45" t="s">
         <v>135</v>
       </c>
-      <c r="F45" s="3">
-        <v>100</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="F45" s="2">
+        <v>100</v>
+      </c>
+      <c r="G45" s="2">
         <f>F45</f>
         <v>100</v>
       </c>
       <c r="H45" t="b">
         <v>0</v>
       </c>
-      <c r="I45" s="3">
+      <c r="I45" s="2">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
@@ -3090,17 +3100,17 @@
       <c r="E46" t="s">
         <v>138</v>
       </c>
-      <c r="F46" s="3">
-        <v>100</v>
-      </c>
-      <c r="G46" s="3">
+      <c r="F46" s="2">
+        <v>100</v>
+      </c>
+      <c r="G46" s="2">
         <f t="shared" si="3"/>
         <v>200</v>
       </c>
       <c r="H46" t="b">
         <v>0</v>
       </c>
-      <c r="I46" s="3">
+      <c r="I46" s="2">
         <f t="shared" si="1"/>
         <v>200</v>
       </c>
@@ -3121,17 +3131,17 @@
       <c r="E47" t="s">
         <v>141</v>
       </c>
-      <c r="F47" s="3">
-        <v>100</v>
-      </c>
-      <c r="G47" s="3">
+      <c r="F47" s="2">
+        <v>100</v>
+      </c>
+      <c r="G47" s="2">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
       <c r="H47" t="b">
         <v>0</v>
       </c>
-      <c r="I47" s="3">
+      <c r="I47" s="2">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
@@ -3152,17 +3162,17 @@
       <c r="E48" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="F48" s="3">
+      <c r="F48" s="2">
         <v>110</v>
       </c>
-      <c r="G48" s="3">
+      <c r="G48" s="2">
         <f t="shared" si="3"/>
         <v>110</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
       </c>
-      <c r="I48" s="3">
+      <c r="I48" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3183,17 +3193,17 @@
       <c r="E49" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="F49" s="3">
+      <c r="F49" s="2">
         <v>50</v>
       </c>
-      <c r="G49" s="3">
+      <c r="G49" s="2">
         <f t="shared" si="3"/>
         <v>50</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
       </c>
-      <c r="I49" s="3">
+      <c r="I49" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3214,17 +3224,17 @@
       <c r="E50" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="F50" s="3">
-        <v>100</v>
-      </c>
-      <c r="G50" s="3">
+      <c r="F50" s="2">
+        <v>100</v>
+      </c>
+      <c r="G50" s="2">
         <f>F50</f>
         <v>100</v>
       </c>
       <c r="H50" t="b">
         <v>1</v>
       </c>
-      <c r="I50" s="3">
+      <c r="I50" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3245,17 +3255,17 @@
       <c r="E51" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="F51" s="3">
+      <c r="F51" s="2">
         <v>25</v>
       </c>
-      <c r="G51" s="3">
+      <c r="G51" s="2">
         <f>F51</f>
         <v>25</v>
       </c>
       <c r="H51" t="b">
         <v>0</v>
       </c>
-      <c r="I51" s="3">
+      <c r="I51" s="2">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
@@ -3276,17 +3286,17 @@
       <c r="E52" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="F52" s="3">
+      <c r="F52" s="2">
         <v>60</v>
       </c>
-      <c r="G52" s="3">
+      <c r="G52" s="2">
         <f t="shared" si="3"/>
         <v>120</v>
       </c>
       <c r="H52" t="b">
         <v>0</v>
       </c>
-      <c r="I52" s="3">
+      <c r="I52" s="2">
         <f t="shared" si="1"/>
         <v>120</v>
       </c>
@@ -3307,17 +3317,17 @@
       <c r="E53" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="F53" s="3">
+      <c r="F53" s="2">
         <v>401</v>
       </c>
-      <c r="G53" s="3">
+      <c r="G53" s="2">
         <f t="shared" si="3"/>
         <v>401</v>
       </c>
       <c r="H53" t="b">
         <v>0</v>
       </c>
-      <c r="I53" s="3">
+      <c r="I53" s="2">
         <f t="shared" si="1"/>
         <v>401</v>
       </c>
@@ -3338,17 +3348,17 @@
       <c r="E54" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="F54" s="3">
+      <c r="F54" s="2">
         <v>30</v>
       </c>
-      <c r="G54" s="3">
+      <c r="G54" s="2">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="H54" t="b">
         <v>1</v>
       </c>
-      <c r="I54" s="3">
+      <c r="I54" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3369,17 +3379,17 @@
       <c r="E55" t="s">
         <v>160</v>
       </c>
-      <c r="F55" s="3">
+      <c r="F55" s="2">
         <v>30</v>
       </c>
-      <c r="G55" s="3">
+      <c r="G55" s="2">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="H55" t="b">
         <v>1</v>
       </c>
-      <c r="I55" s="3">
+      <c r="I55" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3400,17 +3410,17 @@
       <c r="E56" t="s">
         <v>160</v>
       </c>
-      <c r="F56" s="3">
+      <c r="F56" s="2">
         <v>30</v>
       </c>
-      <c r="G56" s="3">
+      <c r="G56" s="2">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="H56" t="b">
         <v>1</v>
       </c>
-      <c r="I56" s="3">
+      <c r="I56" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3431,17 +3441,17 @@
       <c r="E57" t="s">
         <v>160</v>
       </c>
-      <c r="F57" s="3">
+      <c r="F57" s="2">
         <v>30</v>
       </c>
-      <c r="G57" s="3">
+      <c r="G57" s="2">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="H57" t="b">
         <v>1</v>
       </c>
-      <c r="I57" s="3">
+      <c r="I57" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3462,17 +3472,17 @@
       <c r="E58" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="F58" s="3">
+      <c r="F58" s="2">
         <v>149</v>
       </c>
-      <c r="G58" s="3">
+      <c r="G58" s="2">
         <f t="shared" si="3"/>
         <v>149</v>
       </c>
       <c r="H58" t="b">
         <v>0</v>
       </c>
-      <c r="I58" s="3">
+      <c r="I58" s="2">
         <f t="shared" si="1"/>
         <v>149</v>
       </c>
@@ -3493,17 +3503,17 @@
       <c r="E59" t="s">
         <v>86</v>
       </c>
-      <c r="F59" s="3">
-        <v>0</v>
-      </c>
-      <c r="G59" s="3">
+      <c r="F59" s="2">
+        <v>0</v>
+      </c>
+      <c r="G59" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H59" t="b">
         <v>1</v>
       </c>
-      <c r="I59" s="3">
+      <c r="I59" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3524,17 +3534,17 @@
       <c r="E60" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="F60" s="3">
+      <c r="F60" s="2">
         <v>110</v>
       </c>
-      <c r="G60" s="3">
+      <c r="G60" s="2">
         <f t="shared" si="3"/>
         <v>110</v>
       </c>
       <c r="H60" t="b">
         <v>0</v>
       </c>
-      <c r="I60" s="3">
+      <c r="I60" s="2">
         <f t="shared" si="1"/>
         <v>110</v>
       </c>
@@ -3555,24 +3565,24 @@
       <c r="E61" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="F61" s="3">
+      <c r="F61" s="2">
         <v>60</v>
       </c>
-      <c r="G61" s="3">
+      <c r="G61" s="2">
         <f t="shared" si="3"/>
         <v>60</v>
       </c>
       <c r="H61" t="b">
         <v>0</v>
       </c>
-      <c r="I61" s="3">
+      <c r="I61" s="2">
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18"/>
-  <dataValidations disablePrompts="1" count="1">
+  <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H61" xr:uid="{7EB1AC05-8B8A-4291-93B5-D00C194BAB7A}">
       <formula1>$K$1:$K$2</formula1>
     </dataValidation>
